--- a/Assets/Document/配置表表头/事件池表头.xlsx
+++ b/Assets/Document/配置表表头/事件池表头.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="14580" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
     <t>消耗AP</t>
   </si>
   <si>
-    <t>要求NPC_ID</t>
+    <t>事件标号</t>
   </si>
   <si>
     <t>是否会显示（解锁条件）</t>
@@ -79,7 +79,7 @@
     <t>CostAP</t>
   </si>
   <si>
-    <t>ReqNpcId</t>
+    <t>EventNum</t>
   </si>
   <si>
     <t>VisibleConditions</t>
@@ -1124,7 +1124,7 @@
         <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
